--- a/excel_templates/settlement statement.xlsx
+++ b/excel_templates/settlement statement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15105" windowHeight="8070"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="结算单" sheetId="18" r:id="rId1"/>
@@ -35,13 +35,13 @@
     <t>委托单位</t>
   </si>
   <si>
-    <t>{{Proxy client}}</t>
+    <t>{{Proxy_client}}</t>
   </si>
   <si>
     <t xml:space="preserve">协议号    </t>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
     <t>日期</t>
@@ -59,19 +59,19 @@
     <t>进口国别</t>
   </si>
   <si>
-    <t>{{importing country}}</t>
-  </si>
-  <si>
-    <t>{{terms}}{{port of destination}}</t>
+    <t>{{importing_country}}</t>
+  </si>
+  <si>
+    <t>{{terms}}{{port_of_destination}}</t>
   </si>
   <si>
     <t>起运港</t>
   </si>
   <si>
-    <t>{{importing country}}港口</t>
-  </si>
-  <si>
-    <t>{{port of destination}}</t>
+    <t>{{importing_country}}港口</t>
+  </si>
+  <si>
+    <t>{{port_of_destination}}</t>
   </si>
   <si>
     <t>核销单编号</t>
@@ -104,7 +104,7 @@
     <t>预计到货金额</t>
   </si>
   <si>
-    <t>{{Payment method}}</t>
+    <t>{{Payment_method}}</t>
   </si>
   <si>
     <t>收入款项明细</t>
@@ -140,7 +140,7 @@
     <t>垫税利息</t>
   </si>
   <si>
-    <t>付汇金额${{unit price}}*{{quantity}}</t>
+    <t>付汇金额${{unit_price}}*{{quantity}}</t>
   </si>
   <si>
     <t>销售费用$1530</t>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="H3" s="11">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/excel_templates/settlement statement.xlsx
+++ b/excel_templates/settlement statement.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">协议号    </t>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>日期</t>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="H3" s="11">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/excel_templates/settlement statement.xlsx
+++ b/excel_templates/settlement statement.xlsx
@@ -62,7 +62,7 @@
     <t>{{importing_country}}</t>
   </si>
   <si>
-    <t>{{terms}}{{port_of_destination}}</t>
+    <t>{{terms}} {{port_of_destination}}</t>
   </si>
   <si>
     <t>起运港</t>
